--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484866_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484866_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9745</v>
+        <v>6.2438</v>
       </c>
       <c r="E2" t="n">
-        <v>3.971</v>
+        <v>4.4783</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0035</v>
+        <v>1.7654</v>
       </c>
       <c r="G2" t="n">
         <v>-1.9876</v>
@@ -610,13 +610,13 @@
         <v>2.4531</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1475</v>
+        <v>0.4168</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7449</v>
+        <v>0.5068</v>
       </c>
       <c r="V2" t="n">
         <v>6.4937</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GARCIA RUIZ</t>
+          <t>V. VICENT TORTOSA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5673</v>
+        <v>5.4313</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8729</v>
+        <v>4.252</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6944</v>
+        <v>1.1793</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5582</v>
+        <v>3.5243</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9088</v>
+        <v>2.4464</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3506</v>
+        <v>1.0779</v>
       </c>
       <c r="J3" t="n">
-        <v>1.847</v>
+        <v>3.6175</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4143</v>
+        <v>2.3666</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5673</v>
+        <v>1.2509</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2888</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5054999999999999</v>
+        <v>0.0798</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2167</v>
+        <v>-0.173</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3774</v>
+        <v>1.6983</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2644</v>
+        <v>1.6983</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3638</v>
+        <v>-0.7347</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0451</v>
+        <v>-0.2709</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3187</v>
+        <v>-0.4638</v>
       </c>
       <c r="V3" t="n">
-        <v>1.268</v>
+        <v>0.9434</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8678</v>
+        <v>0.9054</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5998</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. VICENT TORTOSA</t>
+          <t>A. GARCIA RUIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3171</v>
+        <v>3.9761</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3495</v>
+        <v>1.996</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9677</v>
+        <v>1.9801</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5243</v>
+        <v>1.5582</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4464</v>
+        <v>1.9088</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0779</v>
+        <v>-0.3506</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6175</v>
+        <v>1.847</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3666</v>
+        <v>2.4143</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2509</v>
+        <v>-0.5673</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.2888</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0798</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.173</v>
+        <v>0.2167</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6983</v>
+        <v>0.3774</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6983</v>
+        <v>2.2644</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8489</v>
+        <v>0.7726</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1735</v>
+        <v>0.1682</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6754</v>
+        <v>0.6044</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9434</v>
+        <v>1.268</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9054</v>
+        <v>1.8678</v>
       </c>
       <c r="X4" t="n">
-        <v>0.038</v>
+        <v>-0.5998</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4015</v>
+        <v>0.8198</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.827</v>
+        <v>-0.5145</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2285</v>
+        <v>1.3343</v>
       </c>
       <c r="G5" t="n">
         <v>1.3142</v>
@@ -844,13 +844,13 @@
         <v>1.6983</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5543</v>
+        <v>-0.1361</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.458</v>
+        <v>-0.1455</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0964</v>
+        <v>0.0094</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9244</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3541</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6382</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9923999999999999</v>
+        <v>1.0453</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1005</v>
@@ -922,13 +922,13 @@
         <v>0.1887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0359</v>
+        <v>0.1145</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3527</v>
+        <v>-0.2553</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3169</v>
+        <v>0.3698</v>
       </c>
       <c r="V6" t="n">
         <v>0.3018</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3034</v>
+        <v>0.3751</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1816</v>
+        <v>-0.0905</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1218</v>
+        <v>0.4657</v>
       </c>
       <c r="G7" t="n">
         <v>0.3573</v>
@@ -1000,13 +1000,13 @@
         <v>3.0192</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0959</v>
+        <v>-0.0241</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4079</v>
+        <v>0.1357</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5038</v>
+        <v>-0.1598</v>
       </c>
       <c r="V7" t="n">
         <v>-1.845</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2333</v>
+        <v>0.1307</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2569</v>
+        <v>-2.2368</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0236</v>
+        <v>2.3675</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2432</v>
@@ -1078,13 +1078,13 @@
         <v>2.8305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7113</v>
+        <v>-0.3473</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4427</v>
+        <v>-0.4226</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2686</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9206</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5173</v>
+        <v>-0.1255</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2819</v>
+        <v>0.0305</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2354</v>
+        <v>-0.156</v>
       </c>
       <c r="G9" t="n">
         <v>0.1632</v>
@@ -1156,13 +1156,13 @@
         <v>1.6983</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6431</v>
+        <v>-0.2513</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5879</v>
+        <v>-0.2754</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0552</v>
+        <v>0.0241</v>
       </c>
       <c r="V9" t="n">
         <v>-1.547</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5336</v>
+        <v>-2.9123</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5471</v>
+        <v>-3.4496</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0135</v>
+        <v>0.5373</v>
       </c>
       <c r="G10" t="n">
         <v>-3.6386</v>
@@ -1234,13 +1234,13 @@
         <v>2.0757</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6108</v>
+        <v>0.2321</v>
       </c>
       <c r="T10" t="n">
-        <v>0.111</v>
+        <v>0.2085</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4998</v>
+        <v>0.0236</v>
       </c>
       <c r="V10" t="n">
         <v>1.249</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.457700000000001</v>
+        <v>-7.6796</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.1472</v>
+        <v>-6.6601</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3105</v>
+        <v>-1.0195</v>
       </c>
       <c r="G11" t="n">
         <v>-5.2003</v>
@@ -1312,13 +1312,13 @@
         <v>1.887</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4085</v>
+        <v>-0.6303</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5632</v>
+        <v>-0.076</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8453000000000001</v>
+        <v>-0.5543</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9054</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.176</v>
+        <v>6.763899999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.323300000000001</v>
+        <v>-2.7355</v>
       </c>
       <c r="F12" t="n">
-        <v>9.499500000000001</v>
+        <v>9.4994</v>
       </c>
       <c r="G12" t="n">
         <v>-5.253</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.112999999999999</v>
+        <v>-2.113</v>
       </c>
       <c r="I12" t="n">
         <v>-3.1399</v>
@@ -1390,13 +1390,13 @@
         <v>19.8135</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1758</v>
+        <v>-0.5878</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.6113</v>
+        <v>-1.0233</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4356000000000001</v>
+        <v>0.4355</v>
       </c>
       <c r="V12" t="n">
         <v>4.1135</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. FELIZ CAMEAU</t>
+          <t>D. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0197</v>
+        <v>1.3424</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9586</v>
+        <v>0.7012</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9783</v>
+        <v>0.6413</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3553</v>
+        <v>0.2614</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0025</v>
+        <v>0.7615</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3578</v>
+        <v>-0.5001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0819</v>
+        <v>-0.1381</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.0415</v>
+        <v>0.4703</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1234</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2734</v>
+        <v>0.3995</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.961</v>
+        <v>0.2911</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2344</v>
+        <v>0.1083</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0757</v>
+        <v>0.3774</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.1514</v>
+        <v>-1.1322</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0757</v>
+        <v>1.5096</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5441</v>
+        <v>-0.1152</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5453</v>
+        <v>-0.1981</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9989</v>
+        <v>0.0829</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8041</v>
+        <v>0.8189</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5657</v>
+        <v>2.1696</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.3697</v>
+        <v>-1.3507</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. HOLGADO CUELLAR</t>
+          <t>J. MAS MICO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3114</v>
+        <v>-0.4736</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4079</v>
+        <v>1.2192</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2614</v>
+        <v>-0.706</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7615</v>
+        <v>-0.5525</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5001</v>
+        <v>-0.1535</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1381</v>
+        <v>-0.4285</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4703</v>
+        <v>0.18</v>
       </c>
       <c r="L14" t="n">
         <v>-0.6084000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3995</v>
+        <v>-0.2775</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2911</v>
+        <v>-0.7325</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1083</v>
+        <v>0.455</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3774</v>
+        <v>0.7548</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1322</v>
+        <v>-0.1887</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5096</v>
+        <v>0.9435</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7383</v>
+        <v>0.6967</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5879</v>
+        <v>0.1435</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1504</v>
+        <v>0.5532</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8189</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1696</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.3507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MAS MICO</t>
+          <t>M. PEREZ MARCO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6337</v>
+        <v>0.6604</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3762</v>
+        <v>0.1757</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0099</v>
+        <v>0.4847</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.706</v>
+        <v>0.3295</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5525</v>
+        <v>0.1996</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1535</v>
+        <v>0.1299</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4285</v>
+        <v>0.0211</v>
       </c>
       <c r="K15" t="n">
-        <v>0.18</v>
+        <v>0.0211</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6084000000000001</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2775</v>
+        <v>0.3083</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7325</v>
+        <v>0.1784</v>
       </c>
       <c r="O15" t="n">
-        <v>0.455</v>
+        <v>0.1299</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5849</v>
+        <v>0.3309</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2409</v>
+        <v>0.1546</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3439</v>
+        <v>0.1764</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MUÑOZ</t>
+          <t>F. LOPEZ ZOROA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.317</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.317</v>
+        <v>1.4035</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.7709</v>
       </c>
       <c r="G16" t="n">
-        <v>0.317</v>
+        <v>3.3213</v>
       </c>
       <c r="H16" t="n">
-        <v>0.317</v>
+        <v>0.99</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2.3314</v>
       </c>
       <c r="J16" t="n">
-        <v>0.317</v>
+        <v>2.9493</v>
       </c>
       <c r="K16" t="n">
-        <v>0.317</v>
+        <v>1.0729</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.8764</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.372</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.0829</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.379</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.3946</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-3.2565</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.019</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-3.2375</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PEREZ MARCO</t>
+          <t>J. MARTINEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1649</v>
+        <v>0.317</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.214</v>
+        <v>0.317</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3789</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3295</v>
+        <v>0.317</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1996</v>
+        <v>0.317</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1299</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0211</v>
+        <v>0.317</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0211</v>
+        <v>0.317</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3083</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1784</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1299</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1646</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2352</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07049999999999999</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0424</v>
+        <v>-0.3497</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0204</v>
+        <v>-2.7999</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0628</v>
+        <v>2.4502</v>
       </c>
       <c r="G18" t="n">
         <v>0.9136</v>
@@ -1858,13 +1858,13 @@
         <v>2.2644</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4802</v>
+        <v>1.0881</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9522</v>
+        <v>0.1727</v>
       </c>
       <c r="U18" t="n">
-        <v>0.528</v>
+        <v>0.9154</v>
       </c>
       <c r="V18" t="n">
         <v>0.4791</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. LOPEZ ZOROA</t>
+          <t>N. FELIZ CAMEAU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2443</v>
+        <v>-0.7171</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9163</v>
+        <v>-2.7124</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1607</v>
+        <v>1.9953</v>
       </c>
       <c r="G19" t="n">
-        <v>3.3213</v>
+        <v>0.3553</v>
       </c>
       <c r="H19" t="n">
-        <v>0.99</v>
+        <v>-1.0025</v>
       </c>
       <c r="I19" t="n">
-        <v>2.3314</v>
+        <v>1.3578</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9493</v>
+        <v>0.0819</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0729</v>
+        <v>-0.0415</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8764</v>
+        <v>0.1234</v>
       </c>
       <c r="M19" t="n">
-        <v>0.372</v>
+        <v>0.2734</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0829</v>
+        <v>-0.961</v>
       </c>
       <c r="O19" t="n">
-        <v>0.455</v>
+        <v>1.2344</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1887</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1322</v>
+        <v>-4.1514</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3209</v>
+        <v>2.0757</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4979</v>
+        <v>1.8073</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8818</v>
+        <v>0.7914</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3839</v>
+        <v>1.0159</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.2565</v>
+        <v>-0.8041</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.019</v>
+        <v>0.5657</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.2375</v>
+        <v>-1.3697</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4924</v>
+        <v>-1.2739</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9739</v>
+        <v>-2.4867</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4815</v>
+        <v>1.2128</v>
       </c>
       <c r="G20" t="n">
         <v>0.0188</v>
@@ -2014,13 +2014,13 @@
         <v>1.3209</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2168</v>
+        <v>0.0016</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7055</v>
+        <v>-0.2183</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5114</v>
+        <v>0.2199</v>
       </c>
       <c r="V20" t="n">
         <v>0.2152</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0222</v>
+        <v>-2.2367</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3288</v>
+        <v>-1.6467</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6934</v>
+        <v>-0.5899</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1304</v>
@@ -2092,13 +2092,13 @@
         <v>0.9435</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6084000000000001</v>
+        <v>0.1771</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.823</v>
+        <v>-0.141</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2146</v>
+        <v>0.3181</v>
       </c>
       <c r="V21" t="n">
         <v>-0.019</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3142</v>
+        <v>-2.6985</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1722</v>
+        <v>-1.9774</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.142</v>
+        <v>-0.7211</v>
       </c>
       <c r="G22" t="n">
         <v>0.5724</v>
@@ -2170,13 +2170,13 @@
         <v>0.9435</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2075</v>
+        <v>-0.5917</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9406</v>
+        <v>-0.7457</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2669</v>
+        <v>0.154</v>
       </c>
       <c r="V22" t="n">
         <v>-1.547</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.1761</v>
+        <v>-3.578</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.499400000000001</v>
+        <v>-9.4993</v>
       </c>
       <c r="F23" t="n">
-        <v>3.323199999999999</v>
+        <v>5.921600000000001</v>
       </c>
       <c r="G23" t="n">
         <v>5.2529</v>
@@ -2248,19 +2248,19 @@
         <v>11.322</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1757</v>
+        <v>3.7738</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4355999999999997</v>
+        <v>-0.4355000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>1.6111</v>
+        <v>4.2095</v>
       </c>
       <c r="V23" t="n">
         <v>-4.1134</v>
       </c>
       <c r="W23" t="n">
-        <v>6.998600000000001</v>
+        <v>6.9986</v>
       </c>
       <c r="X23" t="n">
         <v>-11.1119</v>
